--- a/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
@@ -600,11 +600,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чистка Air Flow</t>
+          <t xml:space="preserve">Комплексная гигиена с брекетами</t>
         </is>
       </c>
       <c r="B30">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -613,98 +613,98 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
+          <t xml:space="preserve">Профессиональная чистка при установленной брекет-системе: ультразвук, Air Flow, полировка.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
+          <t xml:space="preserve">Комплексная гигиена с ретейнерами</t>
         </is>
       </c>
       <c r="B31">
-        <v>8500</v>
+        <v>7000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
+          <t xml:space="preserve">Профессиональная чистка при установленных ретейнерах: ультразвук, Air Flow, полировка.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
+          <t xml:space="preserve">Чистка Air Flow</t>
         </is>
       </c>
       <c r="B32">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
+          <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба</t>
+          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
         </is>
       </c>
       <c r="B33">
-        <v>1500</v>
+        <v>8500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
+          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цветная пломба Twinky Star</t>
+          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
         </is>
       </c>
       <c r="B34">
-        <v>2800</v>
+        <v>4500</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
+          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба</t>
+          <t xml:space="preserve">Лечение молочного зуба</t>
         </is>
       </c>
       <c r="B35">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -713,18 +713,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
+          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консультация детского стоматолога</t>
+          <t xml:space="preserve">Цветная пломба Twinky Star</t>
         </is>
       </c>
       <c r="B36">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -733,57 +733,59 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
+          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: КТ + план лечения</t>
+          <t xml:space="preserve">Удаление молочного зуба</t>
         </is>
       </c>
       <c r="B37">
-        <v>4200</v>
+        <v>1650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
+          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+          <t xml:space="preserve">Консультация детского стоматолога</t>
         </is>
       </c>
       <c r="B38">
-        <v>17500</v>
+        <v>1000</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
-        </is>
-      </c>
-      <c r="B39"/>
+          <t xml:space="preserve">Акция: КТ + план лечения</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>4200</v>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -791,17 +793,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
-        </is>
-      </c>
-      <c r="B40"/>
+          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>17500</v>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -809,14 +813,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
         </is>
       </c>
       <c r="B41"/>
@@ -827,14 +831,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
         </is>
       </c>
       <c r="B42"/>
@@ -844,6 +848,42 @@
         </is>
       </c>
       <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+        </is>
+      </c>
+      <c r="B43"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+        </is>
+      </c>
+      <c r="B44"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
         </is>

--- a/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -660,206 +660,212 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
+          <t xml:space="preserve">Ультразвуковая гигиена</t>
         </is>
       </c>
       <c r="B33">
-        <v>8500</v>
+        <v>2500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
+          <t xml:space="preserve">Снятие зубного камня ультразвуком.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
+          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы 3–4 мм)</t>
         </is>
       </c>
       <c r="B34">
-        <v>4500</v>
+        <v>7500</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
+          <t xml:space="preserve">Комплексная гигиена с глубоким кюретажем пародонтальных карманов 3–4 мм.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба</t>
+          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы от 5 мм)</t>
         </is>
       </c>
       <c r="B35">
-        <v>1500</v>
+        <v>9500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
+          <t xml:space="preserve">Комплексная гигиена с глубоким кюретажем пародонтальных карманов от 5 мм.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цветная пломба Twinky Star</t>
+          <t xml:space="preserve">Глубокое фторирование</t>
         </is>
       </c>
       <c r="B36">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
+          <t xml:space="preserve">Укрепление эмали всех зубов: фторирующий гель в каппах.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба</t>
+          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
         </is>
       </c>
       <c r="B37">
-        <v>1650</v>
+        <v>8500</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
+          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консультация детского стоматолога</t>
+          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
         </is>
       </c>
       <c r="B38">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
+          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: КТ + план лечения</t>
+          <t xml:space="preserve">Лечение молочного зуба</t>
         </is>
       </c>
       <c r="B39">
-        <v>4200</v>
+        <v>1500</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
+          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+          <t xml:space="preserve">Цветная пломба Twinky Star</t>
         </is>
       </c>
       <c r="B40">
-        <v>17500</v>
+        <v>2800</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
-        </is>
-      </c>
-      <c r="B41"/>
+          <t xml:space="preserve">Удаление молочного зуба</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1650</v>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
-        </is>
-      </c>
-      <c r="B42"/>
+          <t xml:space="preserve">Консультация детского стоматолога</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1000</v>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
-        </is>
-      </c>
-      <c r="B43"/>
+          <t xml:space="preserve">Акция: КТ + план лечения</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>4200</v>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -867,23 +873,97 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>17500</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
+        </is>
+      </c>
+      <c r="B45"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
+        </is>
+      </c>
+      <c r="B46"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+        </is>
+      </c>
+      <c r="B47"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
         </is>
       </c>
-      <c r="B44"/>
-      <c r="C44" t="inlineStr">
+      <c r="B48"/>
+      <c r="C48" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
         </is>

--- a/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/versal-dent-yandex-business-price.xlsx
@@ -680,7 +680,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы 3–4 мм)</t>
+          <t xml:space="preserve">Гигиена + чистка десневых карманов 3–4 мм (кюретаж)</t>
         </is>
       </c>
       <c r="B34">
@@ -700,7 +700,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы от 5 мм)</t>
+          <t xml:space="preserve">Гигиена + чистка десневых карманов от 5 мм (кюретаж)</t>
         </is>
       </c>
       <c r="B35">
